--- a/prolongation_report.xlsx
+++ b/prolongation_report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="64">
   <si>
     <t>Отчёт о пролонгациях — 2023 год</t>
   </si>
@@ -113,7 +113,7 @@
     <t>К1 — пролонгация в 1-й месяц; К2 — пролонгация во 2-й месяц (среди не пролонгировавшихся в 1-й). Цвет: красный → жёлтый → зелёный.</t>
   </si>
   <si>
-    <t>Декабрь 2022</t>
+    <t>Декабрь '22</t>
   </si>
   <si>
     <t>Январь</t>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>Декабрь</t>
+  </si>
+  <si>
+    <t>Январь '24</t>
   </si>
   <si>
     <t>2023 год</t>
@@ -419,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -463,11 +466,17 @@
     <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -556,11 +565,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -594,16 +603,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$4:$M$4</c:f>
+              <c:f>'График К1'!$B$4:$O$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.6475900997325404</c:v>
                 </c:pt>
@@ -639,6 +654,12 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.5178822667639573</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.5445954213860255</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.4653954223599074</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -671,11 +692,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -709,16 +730,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$5:$M$5</c:f>
+              <c:f>'График К1'!$B$5:$O$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.3563549567334689</c:v>
                 </c:pt>
@@ -754,6 +781,12 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.6210006947226171</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.3240631628564695</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.5354083873128556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -786,11 +819,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -824,16 +857,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$6:$M$6</c:f>
+              <c:f>'График К1'!$B$6:$O$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -868,6 +907,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -901,11 +946,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -939,16 +984,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$7:$M$7</c:f>
+              <c:f>'График К1'!$B$7:$O$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -984,6 +1035,12 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.4736414793704891</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.2740116643550536</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.5887812742256039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1016,11 +1073,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -1054,16 +1111,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$8:$M$8</c:f>
+              <c:f>'График К1'!$B$8:$O$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.9062563648954557</c:v>
                 </c:pt>
@@ -1098,6 +1161,12 @@
                   <c:v>0.4490783646250567</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1131,11 +1200,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -1169,16 +1238,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$9:$M$9</c:f>
+              <c:f>'График К1'!$B$9:$O$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1213,6 +1288,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.111181821873858</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1246,11 +1327,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -1284,16 +1365,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$10:$M$10</c:f>
+              <c:f>'График К1'!$B$10:$O$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.2958266917837994</c:v>
                 </c:pt>
@@ -1329,6 +1416,12 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.6001238280558995</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.4309066821066209</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1361,11 +1454,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -1399,16 +1492,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$11:$M$11</c:f>
+              <c:f>'График К1'!$B$11:$O$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1444,6 +1543,12 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.8362370621385686</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.3611369711452556</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.4070764865614627</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1476,11 +1581,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -1514,16 +1619,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$12:$M$12</c:f>
+              <c:f>'График К1'!$B$12:$O$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0.8355203065475527</c:v>
                 </c:pt>
@@ -1559,6 +1670,12 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.1786262892253676</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.791061481597168</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3947984301273797</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1591,11 +1708,11 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'График К1'!$B$3:$M$3</c:f>
+              <c:f>'График К1'!$B$3:$O$3</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>Декабрь 2022</c:v>
+                  <c:v>Декабрь '22</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Январь</c:v>
@@ -1629,16 +1746,22 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Ноябрь</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Декабрь</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Январь '24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'График К1'!$B$13:$M$13</c:f>
+              <c:f>'График К1'!$B$13:$O$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1673,6 +1796,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2298,16 +2427,16 @@
       <c r="C16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="15">
         <v>98492</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="15">
         <v>109442.52</v>
       </c>
-      <c r="F16" s="13">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="F16" s="15">
+        <v>0</v>
+      </c>
+      <c r="G16" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2381,25 +2510,25 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="16">
-        <v>0</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="B20" s="17">
+        <v>0</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="18">
         <v>50250</v>
       </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15">
-        <v>0</v>
-      </c>
-      <c r="G20" s="15">
+      <c r="E20" s="18">
+        <v>0</v>
+      </c>
+      <c r="F20" s="18">
+        <v>0</v>
+      </c>
+      <c r="G20" s="18">
         <v>0</v>
       </c>
     </row>
@@ -2411,22 +2540,22 @@
       <c r="C23" s="13"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2454,44 +2583,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
     </row>
     <row r="2" spans="1:16" ht="22" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="6" t="s">
@@ -2537,31 +2666,31 @@
         <v>43</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" s="20" t="s">
         <v>44</v>
       </c>
+      <c r="P4" s="22" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
+      <c r="A5" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="7" t="s">
@@ -2673,7 +2802,7 @@
       <c r="C8" s="11">
         <v>0.2700657835853922</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="11">
@@ -2697,16 +2826,16 @@
       <c r="K8" s="11">
         <v>0.9985489020025152</v>
       </c>
-      <c r="L8" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="22" t="s">
+      <c r="L8" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="24" t="s">
         <v>21</v>
       </c>
       <c r="P8" s="11">
@@ -2717,7 +2846,7 @@
       <c r="A9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="11">
@@ -2726,25 +2855,25 @@
       <c r="D9" s="11">
         <v>0.8469549467964682</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="24" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="11">
         <v>0</v>
       </c>
-      <c r="G9" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="22" t="s">
+      <c r="G9" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="24" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="11">
@@ -2791,7 +2920,7 @@
       <c r="I10" s="11">
         <v>1.197524627431169</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="24" t="s">
         <v>21</v>
       </c>
       <c r="K10" s="11">
@@ -2800,7 +2929,7 @@
       <c r="L10" s="11">
         <v>0.4490783646250567</v>
       </c>
-      <c r="M10" s="22" t="s">
+      <c r="M10" s="24" t="s">
         <v>21</v>
       </c>
       <c r="N10" s="11">
@@ -2817,46 +2946,46 @@
       <c r="A11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="22" t="s">
+      <c r="B11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="24" t="s">
         <v>21</v>
       </c>
       <c r="N11" s="11">
         <v>1.111181821873858</v>
       </c>
-      <c r="O11" s="22" t="s">
+      <c r="O11" s="24" t="s">
         <v>21</v>
       </c>
       <c r="P11" s="11">
@@ -2900,7 +3029,7 @@
       <c r="L12" s="11">
         <v>0.7297423746679665</v>
       </c>
-      <c r="M12" s="22" t="s">
+      <c r="M12" s="24" t="s">
         <v>21</v>
       </c>
       <c r="N12" s="11">
@@ -2917,7 +3046,7 @@
       <c r="A13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="11">
@@ -2926,13 +3055,13 @@
       <c r="D13" s="11">
         <v>0</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="24" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="11">
         <v>0.9661026054257319</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="11">
@@ -3017,43 +3146,43 @@
       <c r="A15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="22" t="s">
+      <c r="B15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="24" t="s">
         <v>21</v>
       </c>
       <c r="O15" s="11">
@@ -3064,24 +3193,24 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
+      <c r="A17" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="7" t="s">
@@ -3137,7 +3266,7 @@
       <c r="A19" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="11">
@@ -3187,7 +3316,7 @@
       <c r="A20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="11">
@@ -3196,7 +3325,7 @@
       <c r="D20" s="11">
         <v>0</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="24" t="s">
         <v>21</v>
       </c>
       <c r="F20" s="11">
@@ -3205,7 +3334,7 @@
       <c r="G20" s="11">
         <v>0</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="24" t="s">
         <v>21</v>
       </c>
       <c r="I20" s="11">
@@ -3217,16 +3346,16 @@
       <c r="K20" s="11">
         <v>0</v>
       </c>
-      <c r="L20" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="22" t="s">
+      <c r="L20" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="24" t="s">
         <v>21</v>
       </c>
       <c r="P20" s="11">
@@ -3237,40 +3366,40 @@
       <c r="A21" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="22" t="s">
+      <c r="B21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="24" t="s">
         <v>21</v>
       </c>
       <c r="G21" s="11">
         <v>0</v>
       </c>
-      <c r="H21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="22" t="s">
+      <c r="H21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="24" t="s">
         <v>21</v>
       </c>
       <c r="N21" s="11">
@@ -3287,7 +3416,7 @@
       <c r="A22" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="11">
@@ -3296,25 +3425,25 @@
       <c r="D22" s="11">
         <v>0</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="22" t="s">
+      <c r="E22" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="24" t="s">
         <v>21</v>
       </c>
       <c r="I22" s="11">
         <v>0</v>
       </c>
-      <c r="J22" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="22" t="s">
+      <c r="J22" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="24" t="s">
         <v>21</v>
       </c>
       <c r="L22" s="11">
@@ -3323,7 +3452,7 @@
       <c r="M22" s="11">
         <v>0</v>
       </c>
-      <c r="N22" s="22" t="s">
+      <c r="N22" s="24" t="s">
         <v>21</v>
       </c>
       <c r="O22" s="11">
@@ -3337,49 +3466,49 @@
       <c r="A23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P23" s="22" t="s">
+      <c r="B23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" s="24" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3387,7 +3516,7 @@
       <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="11">
@@ -3423,7 +3552,7 @@
       <c r="M24" s="11">
         <v>0.1898370470723135</v>
       </c>
-      <c r="N24" s="22" t="s">
+      <c r="N24" s="24" t="s">
         <v>21</v>
       </c>
       <c r="O24" s="11">
@@ -3437,10 +3566,10 @@
       <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="22" t="s">
+      <c r="B25" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="11">
@@ -3449,13 +3578,13 @@
       <c r="E25" s="11">
         <v>1.150520833333333</v>
       </c>
-      <c r="F25" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="22" t="s">
+      <c r="F25" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="24" t="s">
         <v>21</v>
       </c>
       <c r="I25" s="11">
@@ -3487,7 +3616,7 @@
       <c r="A26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="11">
@@ -3537,49 +3666,49 @@
       <c r="A27" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="P27" s="22" t="s">
+      <c r="B27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" s="24" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3616,36 +3745,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1">
-      <c r="A1" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="A1" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="20" customHeight="1">
-      <c r="A2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="A2" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
@@ -3921,38 +4050,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1">
-      <c r="A1" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
+      <c r="A1" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
+      <c r="A3" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="6" t="s">
@@ -3998,53 +4127,53 @@
         <v>43</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="25">
         <v>18</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="25">
         <v>50</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="25">
         <v>15</v>
       </c>
-      <c r="E5" s="23">
-        <v>21</v>
-      </c>
-      <c r="F5" s="23">
+      <c r="E5" s="25">
+        <v>21</v>
+      </c>
+      <c r="F5" s="25">
         <v>30</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="25">
         <v>22</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="25">
         <v>19</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="25">
         <v>27</v>
       </c>
-      <c r="J5" s="23">
-        <v>21</v>
-      </c>
-      <c r="K5" s="23">
+      <c r="J5" s="25">
+        <v>21</v>
+      </c>
+      <c r="K5" s="25">
         <v>24</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="25">
         <v>37</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="25">
         <v>18</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="25">
         <v>26</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="25">
         <v>65</v>
       </c>
     </row>
@@ -4052,46 +4181,46 @@
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="26">
         <v>7</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="26">
         <v>12</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="26">
         <v>3</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="26">
         <v>9</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="26">
         <v>11</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="26">
         <v>9</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="26">
         <v>4</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="26">
         <v>9</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="26">
         <v>5</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="26">
         <v>8</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="26">
         <v>6</v>
       </c>
-      <c r="M6" s="24">
+      <c r="M6" s="26">
         <v>5</v>
       </c>
-      <c r="N6" s="24">
+      <c r="N6" s="26">
         <v>3</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="26">
         <v>17</v>
       </c>
     </row>
@@ -4099,46 +4228,46 @@
       <c r="A7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="24">
-        <v>1</v>
-      </c>
-      <c r="C7" s="24">
+      <c r="B7" s="26">
+        <v>1</v>
+      </c>
+      <c r="C7" s="26">
         <v>14</v>
       </c>
-      <c r="D7" s="24">
-        <v>0</v>
-      </c>
-      <c r="E7" s="24">
+      <c r="D7" s="26">
+        <v>0</v>
+      </c>
+      <c r="E7" s="26">
         <v>2</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="26">
         <v>4</v>
       </c>
-      <c r="G7" s="24">
-        <v>1</v>
-      </c>
-      <c r="H7" s="24">
+      <c r="G7" s="26">
+        <v>1</v>
+      </c>
+      <c r="H7" s="26">
         <v>7</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="26">
         <v>6</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="26">
         <v>4</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="26">
         <v>2</v>
       </c>
-      <c r="L7" s="24">
-        <v>0</v>
-      </c>
-      <c r="M7" s="24">
-        <v>0</v>
-      </c>
-      <c r="N7" s="24">
-        <v>0</v>
-      </c>
-      <c r="O7" s="24">
+      <c r="L7" s="26">
+        <v>0</v>
+      </c>
+      <c r="M7" s="26">
+        <v>0</v>
+      </c>
+      <c r="N7" s="26">
+        <v>0</v>
+      </c>
+      <c r="O7" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4146,46 +4275,46 @@
       <c r="A8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="24">
-        <v>0</v>
-      </c>
-      <c r="C8" s="24">
-        <v>1</v>
-      </c>
-      <c r="D8" s="24">
-        <v>1</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0</v>
-      </c>
-      <c r="F8" s="24">
-        <v>1</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0</v>
-      </c>
-      <c r="H8" s="24">
-        <v>0</v>
-      </c>
-      <c r="I8" s="24">
-        <v>0</v>
-      </c>
-      <c r="J8" s="24">
-        <v>0</v>
-      </c>
-      <c r="K8" s="24">
-        <v>0</v>
-      </c>
-      <c r="L8" s="24">
-        <v>1</v>
-      </c>
-      <c r="M8" s="24">
+      <c r="B8" s="26">
+        <v>0</v>
+      </c>
+      <c r="C8" s="26">
+        <v>1</v>
+      </c>
+      <c r="D8" s="26">
+        <v>1</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0</v>
+      </c>
+      <c r="H8" s="26">
+        <v>0</v>
+      </c>
+      <c r="I8" s="26">
+        <v>0</v>
+      </c>
+      <c r="J8" s="26">
+        <v>0</v>
+      </c>
+      <c r="K8" s="26">
+        <v>0</v>
+      </c>
+      <c r="L8" s="26">
+        <v>1</v>
+      </c>
+      <c r="M8" s="26">
         <v>3</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="26">
         <v>4</v>
       </c>
-      <c r="O8" s="24">
+      <c r="O8" s="26">
         <v>8</v>
       </c>
     </row>
@@ -4193,46 +4322,46 @@
       <c r="A9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="26">
         <v>3</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <v>6</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="26">
         <v>2</v>
       </c>
-      <c r="E9" s="24">
-        <v>1</v>
-      </c>
-      <c r="F9" s="24">
+      <c r="E9" s="26">
+        <v>1</v>
+      </c>
+      <c r="F9" s="26">
         <v>2</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="26">
         <v>2</v>
       </c>
-      <c r="H9" s="24">
-        <v>1</v>
-      </c>
-      <c r="I9" s="24">
-        <v>1</v>
-      </c>
-      <c r="J9" s="24">
-        <v>0</v>
-      </c>
-      <c r="K9" s="24">
-        <v>1</v>
-      </c>
-      <c r="L9" s="24">
+      <c r="H9" s="26">
+        <v>1</v>
+      </c>
+      <c r="I9" s="26">
+        <v>1</v>
+      </c>
+      <c r="J9" s="26">
+        <v>0</v>
+      </c>
+      <c r="K9" s="26">
+        <v>1</v>
+      </c>
+      <c r="L9" s="26">
         <v>4</v>
       </c>
-      <c r="M9" s="24">
-        <v>0</v>
-      </c>
-      <c r="N9" s="24">
-        <v>1</v>
-      </c>
-      <c r="O9" s="24">
+      <c r="M9" s="26">
+        <v>0</v>
+      </c>
+      <c r="N9" s="26">
+        <v>1</v>
+      </c>
+      <c r="O9" s="26">
         <v>1</v>
       </c>
     </row>
@@ -4240,46 +4369,46 @@
       <c r="A10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="24">
-        <v>0</v>
-      </c>
-      <c r="C10" s="24">
-        <v>0</v>
-      </c>
-      <c r="D10" s="24">
-        <v>0</v>
-      </c>
-      <c r="E10" s="24">
-        <v>0</v>
-      </c>
-      <c r="F10" s="24">
-        <v>0</v>
-      </c>
-      <c r="G10" s="24">
-        <v>0</v>
-      </c>
-      <c r="H10" s="24">
-        <v>0</v>
-      </c>
-      <c r="I10" s="24">
-        <v>0</v>
-      </c>
-      <c r="J10" s="24">
-        <v>0</v>
-      </c>
-      <c r="K10" s="24">
-        <v>0</v>
-      </c>
-      <c r="L10" s="24">
-        <v>0</v>
-      </c>
-      <c r="M10" s="24">
-        <v>0</v>
-      </c>
-      <c r="N10" s="24">
-        <v>1</v>
-      </c>
-      <c r="O10" s="24">
+      <c r="B10" s="26">
+        <v>0</v>
+      </c>
+      <c r="C10" s="26">
+        <v>0</v>
+      </c>
+      <c r="D10" s="26">
+        <v>0</v>
+      </c>
+      <c r="E10" s="26">
+        <v>0</v>
+      </c>
+      <c r="F10" s="26">
+        <v>0</v>
+      </c>
+      <c r="G10" s="26">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26">
+        <v>0</v>
+      </c>
+      <c r="I10" s="26">
+        <v>0</v>
+      </c>
+      <c r="J10" s="26">
+        <v>0</v>
+      </c>
+      <c r="K10" s="26">
+        <v>0</v>
+      </c>
+      <c r="L10" s="26">
+        <v>0</v>
+      </c>
+      <c r="M10" s="26">
+        <v>0</v>
+      </c>
+      <c r="N10" s="26">
+        <v>1</v>
+      </c>
+      <c r="O10" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4287,46 +4416,46 @@
       <c r="A11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <v>5</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="26">
         <v>3</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="26">
         <v>5</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="26">
         <v>6</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="26">
         <v>7</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="26">
         <v>2</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="26">
         <v>3</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="26">
         <v>4</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="26">
         <v>4</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="26">
         <v>9</v>
       </c>
-      <c r="M11" s="24">
-        <v>0</v>
-      </c>
-      <c r="N11" s="24">
+      <c r="M11" s="26">
+        <v>0</v>
+      </c>
+      <c r="N11" s="26">
         <v>2</v>
       </c>
-      <c r="O11" s="24">
+      <c r="O11" s="26">
         <v>13</v>
       </c>
     </row>
@@ -4334,46 +4463,46 @@
       <c r="A12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="24">
-        <v>0</v>
-      </c>
-      <c r="C12" s="24">
+      <c r="B12" s="26">
+        <v>0</v>
+      </c>
+      <c r="C12" s="26">
         <v>3</v>
       </c>
-      <c r="D12" s="24">
-        <v>1</v>
-      </c>
-      <c r="E12" s="24">
-        <v>0</v>
-      </c>
-      <c r="F12" s="24">
+      <c r="D12" s="26">
+        <v>1</v>
+      </c>
+      <c r="E12" s="26">
+        <v>0</v>
+      </c>
+      <c r="F12" s="26">
         <v>2</v>
       </c>
-      <c r="G12" s="24">
-        <v>0</v>
-      </c>
-      <c r="H12" s="24">
+      <c r="G12" s="26">
+        <v>0</v>
+      </c>
+      <c r="H12" s="26">
         <v>2</v>
       </c>
-      <c r="I12" s="24">
-        <v>1</v>
-      </c>
-      <c r="J12" s="24">
+      <c r="I12" s="26">
+        <v>1</v>
+      </c>
+      <c r="J12" s="26">
         <v>4</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="26">
         <v>4</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="26">
         <v>7</v>
       </c>
-      <c r="M12" s="24">
+      <c r="M12" s="26">
         <v>7</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="26">
         <v>9</v>
       </c>
-      <c r="O12" s="24">
+      <c r="O12" s="26">
         <v>17</v>
       </c>
     </row>
@@ -4381,46 +4510,46 @@
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="26">
         <v>5</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="26">
         <v>9</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="26">
         <v>5</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="26">
         <v>4</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="26">
         <v>4</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="26">
         <v>3</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="26">
         <v>3</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="26">
         <v>7</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="26">
         <v>4</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13" s="26">
         <v>5</v>
       </c>
-      <c r="L13" s="24">
+      <c r="L13" s="26">
         <v>10</v>
       </c>
-      <c r="M13" s="24">
+      <c r="M13" s="26">
         <v>3</v>
       </c>
-      <c r="N13" s="24">
+      <c r="N13" s="26">
         <v>6</v>
       </c>
-      <c r="O13" s="24">
+      <c r="O13" s="26">
         <v>8</v>
       </c>
     </row>
@@ -4428,65 +4557,65 @@
       <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="24">
-        <v>0</v>
-      </c>
-      <c r="C14" s="24">
-        <v>0</v>
-      </c>
-      <c r="D14" s="24">
-        <v>0</v>
-      </c>
-      <c r="E14" s="24">
-        <v>0</v>
-      </c>
-      <c r="F14" s="24">
-        <v>0</v>
-      </c>
-      <c r="G14" s="24">
-        <v>0</v>
-      </c>
-      <c r="H14" s="24">
-        <v>0</v>
-      </c>
-      <c r="I14" s="24">
-        <v>0</v>
-      </c>
-      <c r="J14" s="24">
-        <v>0</v>
-      </c>
-      <c r="K14" s="24">
-        <v>0</v>
-      </c>
-      <c r="L14" s="24">
-        <v>0</v>
-      </c>
-      <c r="M14" s="24">
-        <v>0</v>
-      </c>
-      <c r="N14" s="24">
-        <v>0</v>
-      </c>
-      <c r="O14" s="24">
+      <c r="B14" s="26">
+        <v>0</v>
+      </c>
+      <c r="C14" s="26">
+        <v>0</v>
+      </c>
+      <c r="D14" s="26">
+        <v>0</v>
+      </c>
+      <c r="E14" s="26">
+        <v>0</v>
+      </c>
+      <c r="F14" s="26">
+        <v>0</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26">
+        <v>0</v>
+      </c>
+      <c r="J14" s="26">
+        <v>0</v>
+      </c>
+      <c r="K14" s="26">
+        <v>0</v>
+      </c>
+      <c r="L14" s="26">
+        <v>0</v>
+      </c>
+      <c r="M14" s="26">
+        <v>0</v>
+      </c>
+      <c r="N14" s="26">
+        <v>0</v>
+      </c>
+      <c r="O14" s="26">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
+      <c r="A16" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="6" t="s">
@@ -4532,53 +4661,53 @@
         <v>43</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="25">
         <v>9</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="25">
         <v>23</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="25">
         <v>5</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="25">
         <v>13</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="25">
         <v>16</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="25">
         <v>16</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="25">
         <v>3</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="25">
         <v>14</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="25">
         <v>12</v>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="25">
         <v>10</v>
       </c>
-      <c r="L18" s="23">
+      <c r="L18" s="25">
         <v>20</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="25">
         <v>10</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="25">
         <v>14</v>
       </c>
-      <c r="O18" s="23">
+      <c r="O18" s="25">
         <v>31</v>
       </c>
     </row>
@@ -4586,46 +4715,46 @@
       <c r="A19" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="26">
         <v>3</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="26">
         <v>6</v>
       </c>
-      <c r="D19" s="24">
-        <v>1</v>
-      </c>
-      <c r="E19" s="24">
+      <c r="D19" s="26">
+        <v>1</v>
+      </c>
+      <c r="E19" s="26">
         <v>5</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="26">
         <v>5</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="26">
         <v>5</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="26">
         <v>2</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="26">
         <v>5</v>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="26">
         <v>3</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K19" s="26">
         <v>3</v>
       </c>
-      <c r="L19" s="24">
-        <v>1</v>
-      </c>
-      <c r="M19" s="24">
+      <c r="L19" s="26">
+        <v>1</v>
+      </c>
+      <c r="M19" s="26">
         <v>3</v>
       </c>
-      <c r="N19" s="24">
-        <v>1</v>
-      </c>
-      <c r="O19" s="24">
+      <c r="N19" s="26">
+        <v>1</v>
+      </c>
+      <c r="O19" s="26">
         <v>11</v>
       </c>
     </row>
@@ -4633,46 +4762,46 @@
       <c r="A20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="24">
-        <v>0</v>
-      </c>
-      <c r="C20" s="24">
+      <c r="B20" s="26">
+        <v>0</v>
+      </c>
+      <c r="C20" s="26">
         <v>4</v>
       </c>
-      <c r="D20" s="24">
-        <v>0</v>
-      </c>
-      <c r="E20" s="24">
-        <v>1</v>
-      </c>
-      <c r="F20" s="24">
+      <c r="D20" s="26">
+        <v>0</v>
+      </c>
+      <c r="E20" s="26">
+        <v>1</v>
+      </c>
+      <c r="F20" s="26">
         <v>2</v>
       </c>
-      <c r="G20" s="24">
-        <v>1</v>
-      </c>
-      <c r="H20" s="24">
-        <v>0</v>
-      </c>
-      <c r="I20" s="24">
+      <c r="G20" s="26">
+        <v>1</v>
+      </c>
+      <c r="H20" s="26">
+        <v>0</v>
+      </c>
+      <c r="I20" s="26">
         <v>2</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="26">
         <v>3</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="26">
         <v>2</v>
       </c>
-      <c r="L20" s="24">
-        <v>0</v>
-      </c>
-      <c r="M20" s="24">
-        <v>0</v>
-      </c>
-      <c r="N20" s="24">
-        <v>0</v>
-      </c>
-      <c r="O20" s="24">
+      <c r="L20" s="26">
+        <v>0</v>
+      </c>
+      <c r="M20" s="26">
+        <v>0</v>
+      </c>
+      <c r="N20" s="26">
+        <v>0</v>
+      </c>
+      <c r="O20" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4680,46 +4809,46 @@
       <c r="A21" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="24">
-        <v>0</v>
-      </c>
-      <c r="C21" s="24">
-        <v>1</v>
-      </c>
-      <c r="D21" s="24">
-        <v>1</v>
-      </c>
-      <c r="E21" s="24">
-        <v>0</v>
-      </c>
-      <c r="F21" s="24">
-        <v>0</v>
-      </c>
-      <c r="G21" s="24">
-        <v>0</v>
-      </c>
-      <c r="H21" s="24">
-        <v>0</v>
-      </c>
-      <c r="I21" s="24">
-        <v>0</v>
-      </c>
-      <c r="J21" s="24">
-        <v>0</v>
-      </c>
-      <c r="K21" s="24">
-        <v>0</v>
-      </c>
-      <c r="L21" s="24">
-        <v>1</v>
-      </c>
-      <c r="M21" s="24">
+      <c r="B21" s="26">
+        <v>0</v>
+      </c>
+      <c r="C21" s="26">
+        <v>1</v>
+      </c>
+      <c r="D21" s="26">
+        <v>1</v>
+      </c>
+      <c r="E21" s="26">
+        <v>0</v>
+      </c>
+      <c r="F21" s="26">
+        <v>0</v>
+      </c>
+      <c r="G21" s="26">
+        <v>0</v>
+      </c>
+      <c r="H21" s="26">
+        <v>0</v>
+      </c>
+      <c r="I21" s="26">
+        <v>0</v>
+      </c>
+      <c r="J21" s="26">
+        <v>0</v>
+      </c>
+      <c r="K21" s="26">
+        <v>0</v>
+      </c>
+      <c r="L21" s="26">
+        <v>1</v>
+      </c>
+      <c r="M21" s="26">
         <v>2</v>
       </c>
-      <c r="N21" s="24">
+      <c r="N21" s="26">
         <v>2</v>
       </c>
-      <c r="O21" s="24">
+      <c r="O21" s="26">
         <v>4</v>
       </c>
     </row>
@@ -4727,46 +4856,46 @@
       <c r="A22" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="26">
         <v>2</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="26">
         <v>4</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="26">
         <v>2</v>
       </c>
-      <c r="E22" s="24">
-        <v>1</v>
-      </c>
-      <c r="F22" s="24">
+      <c r="E22" s="26">
+        <v>1</v>
+      </c>
+      <c r="F22" s="26">
         <v>2</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="26">
         <v>2</v>
       </c>
-      <c r="H22" s="24">
-        <v>0</v>
-      </c>
-      <c r="I22" s="24">
-        <v>1</v>
-      </c>
-      <c r="J22" s="24">
-        <v>0</v>
-      </c>
-      <c r="K22" s="24">
-        <v>0</v>
-      </c>
-      <c r="L22" s="24">
+      <c r="H22" s="26">
+        <v>0</v>
+      </c>
+      <c r="I22" s="26">
+        <v>1</v>
+      </c>
+      <c r="J22" s="26">
+        <v>0</v>
+      </c>
+      <c r="K22" s="26">
+        <v>0</v>
+      </c>
+      <c r="L22" s="26">
         <v>2</v>
       </c>
-      <c r="M22" s="24">
-        <v>0</v>
-      </c>
-      <c r="N22" s="24">
-        <v>0</v>
-      </c>
-      <c r="O22" s="24">
+      <c r="M22" s="26">
+        <v>0</v>
+      </c>
+      <c r="N22" s="26">
+        <v>0</v>
+      </c>
+      <c r="O22" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4774,46 +4903,46 @@
       <c r="A23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="24">
-        <v>0</v>
-      </c>
-      <c r="C23" s="24">
-        <v>0</v>
-      </c>
-      <c r="D23" s="24">
-        <v>0</v>
-      </c>
-      <c r="E23" s="24">
-        <v>0</v>
-      </c>
-      <c r="F23" s="24">
-        <v>0</v>
-      </c>
-      <c r="G23" s="24">
-        <v>0</v>
-      </c>
-      <c r="H23" s="24">
-        <v>0</v>
-      </c>
-      <c r="I23" s="24">
-        <v>0</v>
-      </c>
-      <c r="J23" s="24">
-        <v>0</v>
-      </c>
-      <c r="K23" s="24">
-        <v>0</v>
-      </c>
-      <c r="L23" s="24">
-        <v>0</v>
-      </c>
-      <c r="M23" s="24">
-        <v>0</v>
-      </c>
-      <c r="N23" s="24">
-        <v>1</v>
-      </c>
-      <c r="O23" s="24">
+      <c r="B23" s="26">
+        <v>0</v>
+      </c>
+      <c r="C23" s="26">
+        <v>0</v>
+      </c>
+      <c r="D23" s="26">
+        <v>0</v>
+      </c>
+      <c r="E23" s="26">
+        <v>0</v>
+      </c>
+      <c r="F23" s="26">
+        <v>0</v>
+      </c>
+      <c r="G23" s="26">
+        <v>0</v>
+      </c>
+      <c r="H23" s="26">
+        <v>0</v>
+      </c>
+      <c r="I23" s="26">
+        <v>0</v>
+      </c>
+      <c r="J23" s="26">
+        <v>0</v>
+      </c>
+      <c r="K23" s="26">
+        <v>0</v>
+      </c>
+      <c r="L23" s="26">
+        <v>0</v>
+      </c>
+      <c r="M23" s="26">
+        <v>0</v>
+      </c>
+      <c r="N23" s="26">
+        <v>1</v>
+      </c>
+      <c r="O23" s="26">
         <v>0</v>
       </c>
     </row>
@@ -4821,46 +4950,46 @@
       <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="24">
-        <v>1</v>
-      </c>
-      <c r="C24" s="24">
+      <c r="B24" s="26">
+        <v>1</v>
+      </c>
+      <c r="C24" s="26">
         <v>2</v>
       </c>
-      <c r="D24" s="24">
-        <v>0</v>
-      </c>
-      <c r="E24" s="24">
+      <c r="D24" s="26">
+        <v>0</v>
+      </c>
+      <c r="E24" s="26">
         <v>3</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="26">
         <v>2</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="26">
         <v>6</v>
       </c>
-      <c r="H24" s="24">
-        <v>0</v>
-      </c>
-      <c r="I24" s="24">
-        <v>1</v>
-      </c>
-      <c r="J24" s="24">
+      <c r="H24" s="26">
+        <v>0</v>
+      </c>
+      <c r="I24" s="26">
+        <v>1</v>
+      </c>
+      <c r="J24" s="26">
         <v>2</v>
       </c>
-      <c r="K24" s="24">
-        <v>1</v>
-      </c>
-      <c r="L24" s="24">
+      <c r="K24" s="26">
+        <v>1</v>
+      </c>
+      <c r="L24" s="26">
         <v>6</v>
       </c>
-      <c r="M24" s="24">
-        <v>0</v>
-      </c>
-      <c r="N24" s="24">
-        <v>1</v>
-      </c>
-      <c r="O24" s="24">
+      <c r="M24" s="26">
+        <v>0</v>
+      </c>
+      <c r="N24" s="26">
+        <v>1</v>
+      </c>
+      <c r="O24" s="26">
         <v>6</v>
       </c>
     </row>
@@ -4868,46 +4997,46 @@
       <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="24">
-        <v>0</v>
-      </c>
-      <c r="C25" s="24">
+      <c r="B25" s="26">
+        <v>0</v>
+      </c>
+      <c r="C25" s="26">
         <v>2</v>
       </c>
-      <c r="D25" s="24">
-        <v>0</v>
-      </c>
-      <c r="E25" s="24">
-        <v>0</v>
-      </c>
-      <c r="F25" s="24">
+      <c r="D25" s="26">
+        <v>0</v>
+      </c>
+      <c r="E25" s="26">
+        <v>0</v>
+      </c>
+      <c r="F25" s="26">
         <v>2</v>
       </c>
-      <c r="G25" s="24">
-        <v>0</v>
-      </c>
-      <c r="H25" s="24">
-        <v>0</v>
-      </c>
-      <c r="I25" s="24">
-        <v>0</v>
-      </c>
-      <c r="J25" s="24">
+      <c r="G25" s="26">
+        <v>0</v>
+      </c>
+      <c r="H25" s="26">
+        <v>0</v>
+      </c>
+      <c r="I25" s="26">
+        <v>0</v>
+      </c>
+      <c r="J25" s="26">
         <v>2</v>
       </c>
-      <c r="K25" s="24">
+      <c r="K25" s="26">
         <v>3</v>
       </c>
-      <c r="L25" s="24">
+      <c r="L25" s="26">
         <v>4</v>
       </c>
-      <c r="M25" s="24">
+      <c r="M25" s="26">
         <v>4</v>
       </c>
-      <c r="N25" s="24">
+      <c r="N25" s="26">
         <v>4</v>
       </c>
-      <c r="O25" s="24">
+      <c r="O25" s="26">
         <v>7</v>
       </c>
     </row>
@@ -4915,46 +5044,46 @@
       <c r="A26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="26">
         <v>3</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="26">
         <v>4</v>
       </c>
-      <c r="D26" s="24">
-        <v>1</v>
-      </c>
-      <c r="E26" s="24">
+      <c r="D26" s="26">
+        <v>1</v>
+      </c>
+      <c r="E26" s="26">
         <v>3</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="26">
         <v>3</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="26">
         <v>2</v>
       </c>
-      <c r="H26" s="24">
-        <v>1</v>
-      </c>
-      <c r="I26" s="24">
+      <c r="H26" s="26">
+        <v>1</v>
+      </c>
+      <c r="I26" s="26">
         <v>5</v>
       </c>
-      <c r="J26" s="24">
+      <c r="J26" s="26">
         <v>2</v>
       </c>
-      <c r="K26" s="24">
-        <v>1</v>
-      </c>
-      <c r="L26" s="24">
+      <c r="K26" s="26">
+        <v>1</v>
+      </c>
+      <c r="L26" s="26">
         <v>6</v>
       </c>
-      <c r="M26" s="24">
-        <v>1</v>
-      </c>
-      <c r="N26" s="24">
+      <c r="M26" s="26">
+        <v>1</v>
+      </c>
+      <c r="N26" s="26">
         <v>5</v>
       </c>
-      <c r="O26" s="24">
+      <c r="O26" s="26">
         <v>3</v>
       </c>
     </row>
@@ -4962,65 +5091,65 @@
       <c r="A27" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="24">
-        <v>0</v>
-      </c>
-      <c r="C27" s="24">
-        <v>0</v>
-      </c>
-      <c r="D27" s="24">
-        <v>0</v>
-      </c>
-      <c r="E27" s="24">
-        <v>0</v>
-      </c>
-      <c r="F27" s="24">
-        <v>0</v>
-      </c>
-      <c r="G27" s="24">
-        <v>0</v>
-      </c>
-      <c r="H27" s="24">
-        <v>0</v>
-      </c>
-      <c r="I27" s="24">
-        <v>0</v>
-      </c>
-      <c r="J27" s="24">
-        <v>0</v>
-      </c>
-      <c r="K27" s="24">
-        <v>0</v>
-      </c>
-      <c r="L27" s="24">
-        <v>0</v>
-      </c>
-      <c r="M27" s="24">
-        <v>0</v>
-      </c>
-      <c r="N27" s="24">
-        <v>0</v>
-      </c>
-      <c r="O27" s="24">
+      <c r="B27" s="26">
+        <v>0</v>
+      </c>
+      <c r="C27" s="26">
+        <v>0</v>
+      </c>
+      <c r="D27" s="26">
+        <v>0</v>
+      </c>
+      <c r="E27" s="26">
+        <v>0</v>
+      </c>
+      <c r="F27" s="26">
+        <v>0</v>
+      </c>
+      <c r="G27" s="26">
+        <v>0</v>
+      </c>
+      <c r="H27" s="26">
+        <v>0</v>
+      </c>
+      <c r="I27" s="26">
+        <v>0</v>
+      </c>
+      <c r="J27" s="26">
+        <v>0</v>
+      </c>
+      <c r="K27" s="26">
+        <v>0</v>
+      </c>
+      <c r="L27" s="26">
+        <v>0</v>
+      </c>
+      <c r="M27" s="26">
+        <v>0</v>
+      </c>
+      <c r="N27" s="26">
+        <v>0</v>
+      </c>
+      <c r="O27" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
+      <c r="A29" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="6" t="s">
@@ -5066,53 +5195,53 @@
         <v>43</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="25">
         <v>9</v>
       </c>
-      <c r="C31" s="23">
+      <c r="C31" s="25">
         <v>27</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="25">
         <v>10</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="25">
         <v>8</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="25">
         <v>14</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="25">
         <v>6</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="25">
         <v>16</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="25">
         <v>13</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J31" s="25">
         <v>9</v>
       </c>
-      <c r="K31" s="23">
+      <c r="K31" s="25">
         <v>14</v>
       </c>
-      <c r="L31" s="23">
+      <c r="L31" s="25">
         <v>17</v>
       </c>
-      <c r="M31" s="23">
+      <c r="M31" s="25">
         <v>8</v>
       </c>
-      <c r="N31" s="23">
+      <c r="N31" s="25">
         <v>12</v>
       </c>
-      <c r="O31" s="23">
+      <c r="O31" s="25">
         <v>34</v>
       </c>
     </row>
@@ -5120,46 +5249,46 @@
       <c r="A32" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="26">
         <v>4</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="26">
         <v>6</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="26">
         <v>2</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="26">
         <v>4</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="26">
         <v>6</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="26">
         <v>4</v>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="26">
         <v>2</v>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="26">
         <v>4</v>
       </c>
-      <c r="J32" s="24">
+      <c r="J32" s="26">
         <v>2</v>
       </c>
-      <c r="K32" s="24">
+      <c r="K32" s="26">
         <v>5</v>
       </c>
-      <c r="L32" s="24">
+      <c r="L32" s="26">
         <v>5</v>
       </c>
-      <c r="M32" s="24">
+      <c r="M32" s="26">
         <v>2</v>
       </c>
-      <c r="N32" s="24">
+      <c r="N32" s="26">
         <v>2</v>
       </c>
-      <c r="O32" s="24">
+      <c r="O32" s="26">
         <v>6</v>
       </c>
     </row>
@@ -5167,46 +5296,46 @@
       <c r="A33" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="24">
-        <v>1</v>
-      </c>
-      <c r="C33" s="24">
+      <c r="B33" s="26">
+        <v>1</v>
+      </c>
+      <c r="C33" s="26">
         <v>10</v>
       </c>
-      <c r="D33" s="24">
-        <v>0</v>
-      </c>
-      <c r="E33" s="24">
-        <v>1</v>
-      </c>
-      <c r="F33" s="24">
+      <c r="D33" s="26">
+        <v>0</v>
+      </c>
+      <c r="E33" s="26">
+        <v>1</v>
+      </c>
+      <c r="F33" s="26">
         <v>2</v>
       </c>
-      <c r="G33" s="24">
-        <v>0</v>
-      </c>
-      <c r="H33" s="24">
+      <c r="G33" s="26">
+        <v>0</v>
+      </c>
+      <c r="H33" s="26">
         <v>7</v>
       </c>
-      <c r="I33" s="24">
+      <c r="I33" s="26">
         <v>4</v>
       </c>
-      <c r="J33" s="24">
-        <v>1</v>
-      </c>
-      <c r="K33" s="24">
-        <v>0</v>
-      </c>
-      <c r="L33" s="24">
-        <v>0</v>
-      </c>
-      <c r="M33" s="24">
-        <v>0</v>
-      </c>
-      <c r="N33" s="24">
-        <v>0</v>
-      </c>
-      <c r="O33" s="24">
+      <c r="J33" s="26">
+        <v>1</v>
+      </c>
+      <c r="K33" s="26">
+        <v>0</v>
+      </c>
+      <c r="L33" s="26">
+        <v>0</v>
+      </c>
+      <c r="M33" s="26">
+        <v>0</v>
+      </c>
+      <c r="N33" s="26">
+        <v>0</v>
+      </c>
+      <c r="O33" s="26">
         <v>0</v>
       </c>
     </row>
@@ -5214,46 +5343,46 @@
       <c r="A34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="24">
-        <v>0</v>
-      </c>
-      <c r="C34" s="24">
-        <v>0</v>
-      </c>
-      <c r="D34" s="24">
-        <v>0</v>
-      </c>
-      <c r="E34" s="24">
-        <v>0</v>
-      </c>
-      <c r="F34" s="24">
-        <v>1</v>
-      </c>
-      <c r="G34" s="24">
-        <v>0</v>
-      </c>
-      <c r="H34" s="24">
-        <v>0</v>
-      </c>
-      <c r="I34" s="24">
-        <v>0</v>
-      </c>
-      <c r="J34" s="24">
-        <v>0</v>
-      </c>
-      <c r="K34" s="24">
-        <v>0</v>
-      </c>
-      <c r="L34" s="24">
-        <v>0</v>
-      </c>
-      <c r="M34" s="24">
-        <v>1</v>
-      </c>
-      <c r="N34" s="24">
+      <c r="B34" s="26">
+        <v>0</v>
+      </c>
+      <c r="C34" s="26">
+        <v>0</v>
+      </c>
+      <c r="D34" s="26">
+        <v>0</v>
+      </c>
+      <c r="E34" s="26">
+        <v>0</v>
+      </c>
+      <c r="F34" s="26">
+        <v>1</v>
+      </c>
+      <c r="G34" s="26">
+        <v>0</v>
+      </c>
+      <c r="H34" s="26">
+        <v>0</v>
+      </c>
+      <c r="I34" s="26">
+        <v>0</v>
+      </c>
+      <c r="J34" s="26">
+        <v>0</v>
+      </c>
+      <c r="K34" s="26">
+        <v>0</v>
+      </c>
+      <c r="L34" s="26">
+        <v>0</v>
+      </c>
+      <c r="M34" s="26">
+        <v>1</v>
+      </c>
+      <c r="N34" s="26">
         <v>2</v>
       </c>
-      <c r="O34" s="24">
+      <c r="O34" s="26">
         <v>4</v>
       </c>
     </row>
@@ -5261,46 +5390,46 @@
       <c r="A35" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="24">
-        <v>1</v>
-      </c>
-      <c r="C35" s="24">
+      <c r="B35" s="26">
+        <v>1</v>
+      </c>
+      <c r="C35" s="26">
         <v>2</v>
       </c>
-      <c r="D35" s="24">
-        <v>0</v>
-      </c>
-      <c r="E35" s="24">
-        <v>0</v>
-      </c>
-      <c r="F35" s="24">
-        <v>0</v>
-      </c>
-      <c r="G35" s="24">
-        <v>0</v>
-      </c>
-      <c r="H35" s="24">
-        <v>1</v>
-      </c>
-      <c r="I35" s="24">
-        <v>0</v>
-      </c>
-      <c r="J35" s="24">
-        <v>0</v>
-      </c>
-      <c r="K35" s="24">
-        <v>1</v>
-      </c>
-      <c r="L35" s="24">
+      <c r="D35" s="26">
+        <v>0</v>
+      </c>
+      <c r="E35" s="26">
+        <v>0</v>
+      </c>
+      <c r="F35" s="26">
+        <v>0</v>
+      </c>
+      <c r="G35" s="26">
+        <v>0</v>
+      </c>
+      <c r="H35" s="26">
+        <v>1</v>
+      </c>
+      <c r="I35" s="26">
+        <v>0</v>
+      </c>
+      <c r="J35" s="26">
+        <v>0</v>
+      </c>
+      <c r="K35" s="26">
+        <v>1</v>
+      </c>
+      <c r="L35" s="26">
         <v>2</v>
       </c>
-      <c r="M35" s="24">
-        <v>0</v>
-      </c>
-      <c r="N35" s="24">
-        <v>1</v>
-      </c>
-      <c r="O35" s="24">
+      <c r="M35" s="26">
+        <v>0</v>
+      </c>
+      <c r="N35" s="26">
+        <v>1</v>
+      </c>
+      <c r="O35" s="26">
         <v>1</v>
       </c>
     </row>
@@ -5308,46 +5437,46 @@
       <c r="A36" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="24">
-        <v>0</v>
-      </c>
-      <c r="C36" s="24">
-        <v>0</v>
-      </c>
-      <c r="D36" s="24">
-        <v>0</v>
-      </c>
-      <c r="E36" s="24">
-        <v>0</v>
-      </c>
-      <c r="F36" s="24">
-        <v>0</v>
-      </c>
-      <c r="G36" s="24">
-        <v>0</v>
-      </c>
-      <c r="H36" s="24">
-        <v>0</v>
-      </c>
-      <c r="I36" s="24">
-        <v>0</v>
-      </c>
-      <c r="J36" s="24">
-        <v>0</v>
-      </c>
-      <c r="K36" s="24">
-        <v>0</v>
-      </c>
-      <c r="L36" s="24">
-        <v>0</v>
-      </c>
-      <c r="M36" s="24">
-        <v>0</v>
-      </c>
-      <c r="N36" s="24">
-        <v>0</v>
-      </c>
-      <c r="O36" s="24">
+      <c r="B36" s="26">
+        <v>0</v>
+      </c>
+      <c r="C36" s="26">
+        <v>0</v>
+      </c>
+      <c r="D36" s="26">
+        <v>0</v>
+      </c>
+      <c r="E36" s="26">
+        <v>0</v>
+      </c>
+      <c r="F36" s="26">
+        <v>0</v>
+      </c>
+      <c r="G36" s="26">
+        <v>0</v>
+      </c>
+      <c r="H36" s="26">
+        <v>0</v>
+      </c>
+      <c r="I36" s="26">
+        <v>0</v>
+      </c>
+      <c r="J36" s="26">
+        <v>0</v>
+      </c>
+      <c r="K36" s="26">
+        <v>0</v>
+      </c>
+      <c r="L36" s="26">
+        <v>0</v>
+      </c>
+      <c r="M36" s="26">
+        <v>0</v>
+      </c>
+      <c r="N36" s="26">
+        <v>0</v>
+      </c>
+      <c r="O36" s="26">
         <v>0</v>
       </c>
     </row>
@@ -5355,46 +5484,46 @@
       <c r="A37" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="24">
-        <v>1</v>
-      </c>
-      <c r="C37" s="24">
+      <c r="B37" s="26">
+        <v>1</v>
+      </c>
+      <c r="C37" s="26">
         <v>3</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="26">
         <v>3</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="26">
         <v>2</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="26">
         <v>4</v>
       </c>
-      <c r="G37" s="24">
-        <v>1</v>
-      </c>
-      <c r="H37" s="24">
+      <c r="G37" s="26">
+        <v>1</v>
+      </c>
+      <c r="H37" s="26">
         <v>2</v>
       </c>
-      <c r="I37" s="24">
+      <c r="I37" s="26">
         <v>2</v>
       </c>
-      <c r="J37" s="24">
+      <c r="J37" s="26">
         <v>2</v>
       </c>
-      <c r="K37" s="24">
+      <c r="K37" s="26">
         <v>3</v>
       </c>
-      <c r="L37" s="24">
+      <c r="L37" s="26">
         <v>3</v>
       </c>
-      <c r="M37" s="24">
-        <v>0</v>
-      </c>
-      <c r="N37" s="24">
-        <v>1</v>
-      </c>
-      <c r="O37" s="24">
+      <c r="M37" s="26">
+        <v>0</v>
+      </c>
+      <c r="N37" s="26">
+        <v>1</v>
+      </c>
+      <c r="O37" s="26">
         <v>7</v>
       </c>
     </row>
@@ -5402,46 +5531,46 @@
       <c r="A38" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="24">
-        <v>0</v>
-      </c>
-      <c r="C38" s="24">
-        <v>1</v>
-      </c>
-      <c r="D38" s="24">
-        <v>1</v>
-      </c>
-      <c r="E38" s="24">
-        <v>0</v>
-      </c>
-      <c r="F38" s="24">
-        <v>0</v>
-      </c>
-      <c r="G38" s="24">
-        <v>0</v>
-      </c>
-      <c r="H38" s="24">
+      <c r="B38" s="26">
+        <v>0</v>
+      </c>
+      <c r="C38" s="26">
+        <v>1</v>
+      </c>
+      <c r="D38" s="26">
+        <v>1</v>
+      </c>
+      <c r="E38" s="26">
+        <v>0</v>
+      </c>
+      <c r="F38" s="26">
+        <v>0</v>
+      </c>
+      <c r="G38" s="26">
+        <v>0</v>
+      </c>
+      <c r="H38" s="26">
         <v>2</v>
       </c>
-      <c r="I38" s="24">
-        <v>1</v>
-      </c>
-      <c r="J38" s="24">
+      <c r="I38" s="26">
+        <v>1</v>
+      </c>
+      <c r="J38" s="26">
         <v>2</v>
       </c>
-      <c r="K38" s="24">
-        <v>1</v>
-      </c>
-      <c r="L38" s="24">
+      <c r="K38" s="26">
+        <v>1</v>
+      </c>
+      <c r="L38" s="26">
         <v>3</v>
       </c>
-      <c r="M38" s="24">
+      <c r="M38" s="26">
         <v>3</v>
       </c>
-      <c r="N38" s="24">
+      <c r="N38" s="26">
         <v>5</v>
       </c>
-      <c r="O38" s="24">
+      <c r="O38" s="26">
         <v>10</v>
       </c>
     </row>
@@ -5449,46 +5578,46 @@
       <c r="A39" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="26">
         <v>2</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="26">
         <v>5</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="26">
         <v>4</v>
       </c>
-      <c r="E39" s="24">
-        <v>1</v>
-      </c>
-      <c r="F39" s="24">
-        <v>1</v>
-      </c>
-      <c r="G39" s="24">
-        <v>1</v>
-      </c>
-      <c r="H39" s="24">
+      <c r="E39" s="26">
+        <v>1</v>
+      </c>
+      <c r="F39" s="26">
+        <v>1</v>
+      </c>
+      <c r="G39" s="26">
+        <v>1</v>
+      </c>
+      <c r="H39" s="26">
         <v>2</v>
       </c>
-      <c r="I39" s="24">
+      <c r="I39" s="26">
         <v>2</v>
       </c>
-      <c r="J39" s="24">
+      <c r="J39" s="26">
         <v>2</v>
       </c>
-      <c r="K39" s="24">
+      <c r="K39" s="26">
         <v>4</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="26">
         <v>4</v>
       </c>
-      <c r="M39" s="24">
+      <c r="M39" s="26">
         <v>2</v>
       </c>
-      <c r="N39" s="24">
-        <v>1</v>
-      </c>
-      <c r="O39" s="24">
+      <c r="N39" s="26">
+        <v>1</v>
+      </c>
+      <c r="O39" s="26">
         <v>5</v>
       </c>
     </row>
@@ -5496,65 +5625,65 @@
       <c r="A40" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="24">
-        <v>0</v>
-      </c>
-      <c r="C40" s="24">
-        <v>0</v>
-      </c>
-      <c r="D40" s="24">
-        <v>0</v>
-      </c>
-      <c r="E40" s="24">
-        <v>0</v>
-      </c>
-      <c r="F40" s="24">
-        <v>0</v>
-      </c>
-      <c r="G40" s="24">
-        <v>0</v>
-      </c>
-      <c r="H40" s="24">
-        <v>0</v>
-      </c>
-      <c r="I40" s="24">
-        <v>0</v>
-      </c>
-      <c r="J40" s="24">
-        <v>0</v>
-      </c>
-      <c r="K40" s="24">
-        <v>0</v>
-      </c>
-      <c r="L40" s="24">
-        <v>0</v>
-      </c>
-      <c r="M40" s="24">
-        <v>0</v>
-      </c>
-      <c r="N40" s="24">
-        <v>0</v>
-      </c>
-      <c r="O40" s="24">
+      <c r="B40" s="26">
+        <v>0</v>
+      </c>
+      <c r="C40" s="26">
+        <v>0</v>
+      </c>
+      <c r="D40" s="26">
+        <v>0</v>
+      </c>
+      <c r="E40" s="26">
+        <v>0</v>
+      </c>
+      <c r="F40" s="26">
+        <v>0</v>
+      </c>
+      <c r="G40" s="26">
+        <v>0</v>
+      </c>
+      <c r="H40" s="26">
+        <v>0</v>
+      </c>
+      <c r="I40" s="26">
+        <v>0</v>
+      </c>
+      <c r="J40" s="26">
+        <v>0</v>
+      </c>
+      <c r="K40" s="26">
+        <v>0</v>
+      </c>
+      <c r="L40" s="26">
+        <v>0</v>
+      </c>
+      <c r="M40" s="26">
+        <v>0</v>
+      </c>
+      <c r="N40" s="26">
+        <v>0</v>
+      </c>
+      <c r="O40" s="26">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="21"/>
+      <c r="A42" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="6" t="s">
@@ -5600,53 +5729,53 @@
         <v>43</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="23">
-        <v>0</v>
-      </c>
-      <c r="C44" s="23">
+      <c r="B44" s="25">
+        <v>0</v>
+      </c>
+      <c r="C44" s="25">
         <v>9</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="25">
         <v>27</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="25">
         <v>10</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="25">
         <v>8</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="25">
         <v>14</v>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="25">
         <v>6</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44" s="25">
         <v>16</v>
       </c>
-      <c r="J44" s="23">
+      <c r="J44" s="25">
         <v>13</v>
       </c>
-      <c r="K44" s="23">
+      <c r="K44" s="25">
         <v>9</v>
       </c>
-      <c r="L44" s="23">
+      <c r="L44" s="25">
         <v>14</v>
       </c>
-      <c r="M44" s="23">
+      <c r="M44" s="25">
         <v>17</v>
       </c>
-      <c r="N44" s="23">
+      <c r="N44" s="25">
         <v>8</v>
       </c>
-      <c r="O44" s="23">
+      <c r="O44" s="25">
         <v>12</v>
       </c>
     </row>
@@ -5654,46 +5783,46 @@
       <c r="A45" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="24">
-        <v>0</v>
-      </c>
-      <c r="C45" s="24">
+      <c r="B45" s="26">
+        <v>0</v>
+      </c>
+      <c r="C45" s="26">
         <v>4</v>
       </c>
-      <c r="D45" s="24">
+      <c r="D45" s="26">
         <v>6</v>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="26">
         <v>2</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="26">
         <v>4</v>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="26">
         <v>6</v>
       </c>
-      <c r="H45" s="24">
+      <c r="H45" s="26">
         <v>4</v>
       </c>
-      <c r="I45" s="24">
+      <c r="I45" s="26">
         <v>2</v>
       </c>
-      <c r="J45" s="24">
+      <c r="J45" s="26">
         <v>4</v>
       </c>
-      <c r="K45" s="24">
+      <c r="K45" s="26">
         <v>2</v>
       </c>
-      <c r="L45" s="24">
+      <c r="L45" s="26">
         <v>5</v>
       </c>
-      <c r="M45" s="24">
+      <c r="M45" s="26">
         <v>5</v>
       </c>
-      <c r="N45" s="24">
+      <c r="N45" s="26">
         <v>2</v>
       </c>
-      <c r="O45" s="24">
+      <c r="O45" s="26">
         <v>2</v>
       </c>
     </row>
@@ -5701,46 +5830,46 @@
       <c r="A46" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="24">
-        <v>0</v>
-      </c>
-      <c r="C46" s="24">
-        <v>1</v>
-      </c>
-      <c r="D46" s="24">
+      <c r="B46" s="26">
+        <v>0</v>
+      </c>
+      <c r="C46" s="26">
+        <v>1</v>
+      </c>
+      <c r="D46" s="26">
         <v>10</v>
       </c>
-      <c r="E46" s="24">
-        <v>0</v>
-      </c>
-      <c r="F46" s="24">
-        <v>1</v>
-      </c>
-      <c r="G46" s="24">
+      <c r="E46" s="26">
+        <v>0</v>
+      </c>
+      <c r="F46" s="26">
+        <v>1</v>
+      </c>
+      <c r="G46" s="26">
         <v>2</v>
       </c>
-      <c r="H46" s="24">
-        <v>0</v>
-      </c>
-      <c r="I46" s="24">
+      <c r="H46" s="26">
+        <v>0</v>
+      </c>
+      <c r="I46" s="26">
         <v>7</v>
       </c>
-      <c r="J46" s="24">
+      <c r="J46" s="26">
         <v>4</v>
       </c>
-      <c r="K46" s="24">
-        <v>1</v>
-      </c>
-      <c r="L46" s="24">
-        <v>0</v>
-      </c>
-      <c r="M46" s="24">
-        <v>0</v>
-      </c>
-      <c r="N46" s="24">
-        <v>0</v>
-      </c>
-      <c r="O46" s="24">
+      <c r="K46" s="26">
+        <v>1</v>
+      </c>
+      <c r="L46" s="26">
+        <v>0</v>
+      </c>
+      <c r="M46" s="26">
+        <v>0</v>
+      </c>
+      <c r="N46" s="26">
+        <v>0</v>
+      </c>
+      <c r="O46" s="26">
         <v>0</v>
       </c>
     </row>
@@ -5748,46 +5877,46 @@
       <c r="A47" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="24">
-        <v>0</v>
-      </c>
-      <c r="C47" s="24">
-        <v>0</v>
-      </c>
-      <c r="D47" s="24">
-        <v>0</v>
-      </c>
-      <c r="E47" s="24">
-        <v>0</v>
-      </c>
-      <c r="F47" s="24">
-        <v>0</v>
-      </c>
-      <c r="G47" s="24">
-        <v>1</v>
-      </c>
-      <c r="H47" s="24">
-        <v>0</v>
-      </c>
-      <c r="I47" s="24">
-        <v>0</v>
-      </c>
-      <c r="J47" s="24">
-        <v>0</v>
-      </c>
-      <c r="K47" s="24">
-        <v>0</v>
-      </c>
-      <c r="L47" s="24">
-        <v>0</v>
-      </c>
-      <c r="M47" s="24">
-        <v>0</v>
-      </c>
-      <c r="N47" s="24">
-        <v>1</v>
-      </c>
-      <c r="O47" s="24">
+      <c r="B47" s="26">
+        <v>0</v>
+      </c>
+      <c r="C47" s="26">
+        <v>0</v>
+      </c>
+      <c r="D47" s="26">
+        <v>0</v>
+      </c>
+      <c r="E47" s="26">
+        <v>0</v>
+      </c>
+      <c r="F47" s="26">
+        <v>0</v>
+      </c>
+      <c r="G47" s="26">
+        <v>1</v>
+      </c>
+      <c r="H47" s="26">
+        <v>0</v>
+      </c>
+      <c r="I47" s="26">
+        <v>0</v>
+      </c>
+      <c r="J47" s="26">
+        <v>0</v>
+      </c>
+      <c r="K47" s="26">
+        <v>0</v>
+      </c>
+      <c r="L47" s="26">
+        <v>0</v>
+      </c>
+      <c r="M47" s="26">
+        <v>0</v>
+      </c>
+      <c r="N47" s="26">
+        <v>1</v>
+      </c>
+      <c r="O47" s="26">
         <v>2</v>
       </c>
     </row>
@@ -5795,46 +5924,46 @@
       <c r="A48" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="24">
-        <v>0</v>
-      </c>
-      <c r="C48" s="24">
-        <v>1</v>
-      </c>
-      <c r="D48" s="24">
+      <c r="B48" s="26">
+        <v>0</v>
+      </c>
+      <c r="C48" s="26">
+        <v>1</v>
+      </c>
+      <c r="D48" s="26">
         <v>2</v>
       </c>
-      <c r="E48" s="24">
-        <v>0</v>
-      </c>
-      <c r="F48" s="24">
-        <v>0</v>
-      </c>
-      <c r="G48" s="24">
-        <v>0</v>
-      </c>
-      <c r="H48" s="24">
-        <v>0</v>
-      </c>
-      <c r="I48" s="24">
-        <v>1</v>
-      </c>
-      <c r="J48" s="24">
-        <v>0</v>
-      </c>
-      <c r="K48" s="24">
-        <v>0</v>
-      </c>
-      <c r="L48" s="24">
-        <v>1</v>
-      </c>
-      <c r="M48" s="24">
+      <c r="E48" s="26">
+        <v>0</v>
+      </c>
+      <c r="F48" s="26">
+        <v>0</v>
+      </c>
+      <c r="G48" s="26">
+        <v>0</v>
+      </c>
+      <c r="H48" s="26">
+        <v>0</v>
+      </c>
+      <c r="I48" s="26">
+        <v>1</v>
+      </c>
+      <c r="J48" s="26">
+        <v>0</v>
+      </c>
+      <c r="K48" s="26">
+        <v>0</v>
+      </c>
+      <c r="L48" s="26">
+        <v>1</v>
+      </c>
+      <c r="M48" s="26">
         <v>2</v>
       </c>
-      <c r="N48" s="24">
-        <v>0</v>
-      </c>
-      <c r="O48" s="24">
+      <c r="N48" s="26">
+        <v>0</v>
+      </c>
+      <c r="O48" s="26">
         <v>1</v>
       </c>
     </row>
@@ -5842,46 +5971,46 @@
       <c r="A49" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="24">
-        <v>0</v>
-      </c>
-      <c r="C49" s="24">
-        <v>0</v>
-      </c>
-      <c r="D49" s="24">
-        <v>0</v>
-      </c>
-      <c r="E49" s="24">
-        <v>0</v>
-      </c>
-      <c r="F49" s="24">
-        <v>0</v>
-      </c>
-      <c r="G49" s="24">
-        <v>0</v>
-      </c>
-      <c r="H49" s="24">
-        <v>0</v>
-      </c>
-      <c r="I49" s="24">
-        <v>0</v>
-      </c>
-      <c r="J49" s="24">
-        <v>0</v>
-      </c>
-      <c r="K49" s="24">
-        <v>0</v>
-      </c>
-      <c r="L49" s="24">
-        <v>0</v>
-      </c>
-      <c r="M49" s="24">
-        <v>0</v>
-      </c>
-      <c r="N49" s="24">
-        <v>0</v>
-      </c>
-      <c r="O49" s="24">
+      <c r="B49" s="26">
+        <v>0</v>
+      </c>
+      <c r="C49" s="26">
+        <v>0</v>
+      </c>
+      <c r="D49" s="26">
+        <v>0</v>
+      </c>
+      <c r="E49" s="26">
+        <v>0</v>
+      </c>
+      <c r="F49" s="26">
+        <v>0</v>
+      </c>
+      <c r="G49" s="26">
+        <v>0</v>
+      </c>
+      <c r="H49" s="26">
+        <v>0</v>
+      </c>
+      <c r="I49" s="26">
+        <v>0</v>
+      </c>
+      <c r="J49" s="26">
+        <v>0</v>
+      </c>
+      <c r="K49" s="26">
+        <v>0</v>
+      </c>
+      <c r="L49" s="26">
+        <v>0</v>
+      </c>
+      <c r="M49" s="26">
+        <v>0</v>
+      </c>
+      <c r="N49" s="26">
+        <v>0</v>
+      </c>
+      <c r="O49" s="26">
         <v>0</v>
       </c>
     </row>
@@ -5889,46 +6018,46 @@
       <c r="A50" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="24">
-        <v>0</v>
-      </c>
-      <c r="C50" s="24">
-        <v>1</v>
-      </c>
-      <c r="D50" s="24">
+      <c r="B50" s="26">
+        <v>0</v>
+      </c>
+      <c r="C50" s="26">
+        <v>1</v>
+      </c>
+      <c r="D50" s="26">
         <v>3</v>
       </c>
-      <c r="E50" s="24">
+      <c r="E50" s="26">
         <v>3</v>
       </c>
-      <c r="F50" s="24">
+      <c r="F50" s="26">
         <v>2</v>
       </c>
-      <c r="G50" s="24">
+      <c r="G50" s="26">
         <v>4</v>
       </c>
-      <c r="H50" s="24">
-        <v>1</v>
-      </c>
-      <c r="I50" s="24">
+      <c r="H50" s="26">
+        <v>1</v>
+      </c>
+      <c r="I50" s="26">
         <v>2</v>
       </c>
-      <c r="J50" s="24">
+      <c r="J50" s="26">
         <v>2</v>
       </c>
-      <c r="K50" s="24">
+      <c r="K50" s="26">
         <v>2</v>
       </c>
-      <c r="L50" s="24">
+      <c r="L50" s="26">
         <v>3</v>
       </c>
-      <c r="M50" s="24">
+      <c r="M50" s="26">
         <v>3</v>
       </c>
-      <c r="N50" s="24">
-        <v>0</v>
-      </c>
-      <c r="O50" s="24">
+      <c r="N50" s="26">
+        <v>0</v>
+      </c>
+      <c r="O50" s="26">
         <v>1</v>
       </c>
     </row>
@@ -5936,46 +6065,46 @@
       <c r="A51" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B51" s="24">
-        <v>0</v>
-      </c>
-      <c r="C51" s="24">
-        <v>0</v>
-      </c>
-      <c r="D51" s="24">
-        <v>1</v>
-      </c>
-      <c r="E51" s="24">
-        <v>1</v>
-      </c>
-      <c r="F51" s="24">
-        <v>0</v>
-      </c>
-      <c r="G51" s="24">
-        <v>0</v>
-      </c>
-      <c r="H51" s="24">
-        <v>0</v>
-      </c>
-      <c r="I51" s="24">
+      <c r="B51" s="26">
+        <v>0</v>
+      </c>
+      <c r="C51" s="26">
+        <v>0</v>
+      </c>
+      <c r="D51" s="26">
+        <v>1</v>
+      </c>
+      <c r="E51" s="26">
+        <v>1</v>
+      </c>
+      <c r="F51" s="26">
+        <v>0</v>
+      </c>
+      <c r="G51" s="26">
+        <v>0</v>
+      </c>
+      <c r="H51" s="26">
+        <v>0</v>
+      </c>
+      <c r="I51" s="26">
         <v>2</v>
       </c>
-      <c r="J51" s="24">
-        <v>1</v>
-      </c>
-      <c r="K51" s="24">
+      <c r="J51" s="26">
+        <v>1</v>
+      </c>
+      <c r="K51" s="26">
         <v>2</v>
       </c>
-      <c r="L51" s="24">
-        <v>1</v>
-      </c>
-      <c r="M51" s="24">
+      <c r="L51" s="26">
+        <v>1</v>
+      </c>
+      <c r="M51" s="26">
         <v>3</v>
       </c>
-      <c r="N51" s="24">
+      <c r="N51" s="26">
         <v>3</v>
       </c>
-      <c r="O51" s="24">
+      <c r="O51" s="26">
         <v>5</v>
       </c>
     </row>
@@ -5983,46 +6112,46 @@
       <c r="A52" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B52" s="24">
-        <v>0</v>
-      </c>
-      <c r="C52" s="24">
+      <c r="B52" s="26">
+        <v>0</v>
+      </c>
+      <c r="C52" s="26">
         <v>2</v>
       </c>
-      <c r="D52" s="24">
+      <c r="D52" s="26">
         <v>5</v>
       </c>
-      <c r="E52" s="24">
+      <c r="E52" s="26">
         <v>4</v>
       </c>
-      <c r="F52" s="24">
-        <v>1</v>
-      </c>
-      <c r="G52" s="24">
-        <v>1</v>
-      </c>
-      <c r="H52" s="24">
-        <v>1</v>
-      </c>
-      <c r="I52" s="24">
+      <c r="F52" s="26">
+        <v>1</v>
+      </c>
+      <c r="G52" s="26">
+        <v>1</v>
+      </c>
+      <c r="H52" s="26">
+        <v>1</v>
+      </c>
+      <c r="I52" s="26">
         <v>2</v>
       </c>
-      <c r="J52" s="24">
+      <c r="J52" s="26">
         <v>2</v>
       </c>
-      <c r="K52" s="24">
+      <c r="K52" s="26">
         <v>2</v>
       </c>
-      <c r="L52" s="24">
+      <c r="L52" s="26">
         <v>4</v>
       </c>
-      <c r="M52" s="24">
+      <c r="M52" s="26">
         <v>4</v>
       </c>
-      <c r="N52" s="24">
+      <c r="N52" s="26">
         <v>2</v>
       </c>
-      <c r="O52" s="24">
+      <c r="O52" s="26">
         <v>1</v>
       </c>
     </row>
@@ -6030,65 +6159,65 @@
       <c r="A53" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="24">
-        <v>0</v>
-      </c>
-      <c r="C53" s="24">
-        <v>0</v>
-      </c>
-      <c r="D53" s="24">
-        <v>0</v>
-      </c>
-      <c r="E53" s="24">
-        <v>0</v>
-      </c>
-      <c r="F53" s="24">
-        <v>0</v>
-      </c>
-      <c r="G53" s="24">
-        <v>0</v>
-      </c>
-      <c r="H53" s="24">
-        <v>0</v>
-      </c>
-      <c r="I53" s="24">
-        <v>0</v>
-      </c>
-      <c r="J53" s="24">
-        <v>0</v>
-      </c>
-      <c r="K53" s="24">
-        <v>0</v>
-      </c>
-      <c r="L53" s="24">
-        <v>0</v>
-      </c>
-      <c r="M53" s="24">
-        <v>0</v>
-      </c>
-      <c r="N53" s="24">
-        <v>0</v>
-      </c>
-      <c r="O53" s="24">
+      <c r="B53" s="26">
+        <v>0</v>
+      </c>
+      <c r="C53" s="26">
+        <v>0</v>
+      </c>
+      <c r="D53" s="26">
+        <v>0</v>
+      </c>
+      <c r="E53" s="26">
+        <v>0</v>
+      </c>
+      <c r="F53" s="26">
+        <v>0</v>
+      </c>
+      <c r="G53" s="26">
+        <v>0</v>
+      </c>
+      <c r="H53" s="26">
+        <v>0</v>
+      </c>
+      <c r="I53" s="26">
+        <v>0</v>
+      </c>
+      <c r="J53" s="26">
+        <v>0</v>
+      </c>
+      <c r="K53" s="26">
+        <v>0</v>
+      </c>
+      <c r="L53" s="26">
+        <v>0</v>
+      </c>
+      <c r="M53" s="26">
+        <v>0</v>
+      </c>
+      <c r="N53" s="26">
+        <v>0</v>
+      </c>
+      <c r="O53" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:15">
-      <c r="A55" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
+      <c r="A55" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="23"/>
+      <c r="K55" s="23"/>
+      <c r="L55" s="23"/>
+      <c r="M55" s="23"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="6" t="s">
@@ -6134,53 +6263,53 @@
         <v>43</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:15">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B57" s="23">
-        <v>0</v>
-      </c>
-      <c r="C57" s="23">
-        <v>1</v>
-      </c>
-      <c r="D57" s="23">
+      <c r="B57" s="25">
+        <v>0</v>
+      </c>
+      <c r="C57" s="25">
+        <v>1</v>
+      </c>
+      <c r="D57" s="25">
         <v>4</v>
       </c>
-      <c r="E57" s="23">
+      <c r="E57" s="25">
         <v>2</v>
       </c>
-      <c r="F57" s="23">
+      <c r="F57" s="25">
         <v>2</v>
       </c>
-      <c r="G57" s="23">
-        <v>0</v>
-      </c>
-      <c r="H57" s="23">
-        <v>1</v>
-      </c>
-      <c r="I57" s="23">
-        <v>1</v>
-      </c>
-      <c r="J57" s="23">
-        <v>1</v>
-      </c>
-      <c r="K57" s="23">
-        <v>0</v>
-      </c>
-      <c r="L57" s="23">
+      <c r="G57" s="25">
+        <v>0</v>
+      </c>
+      <c r="H57" s="25">
+        <v>1</v>
+      </c>
+      <c r="I57" s="25">
+        <v>1</v>
+      </c>
+      <c r="J57" s="25">
+        <v>1</v>
+      </c>
+      <c r="K57" s="25">
+        <v>0</v>
+      </c>
+      <c r="L57" s="25">
         <v>2</v>
       </c>
-      <c r="M57" s="23">
-        <v>1</v>
-      </c>
-      <c r="N57" s="23">
+      <c r="M57" s="25">
+        <v>1</v>
+      </c>
+      <c r="N57" s="25">
         <v>2</v>
       </c>
-      <c r="O57" s="23">
+      <c r="O57" s="25">
         <v>2</v>
       </c>
     </row>
@@ -6188,46 +6317,46 @@
       <c r="A58" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B58" s="24">
-        <v>0</v>
-      </c>
-      <c r="C58" s="24">
-        <v>0</v>
-      </c>
-      <c r="D58" s="24">
+      <c r="B58" s="26">
+        <v>0</v>
+      </c>
+      <c r="C58" s="26">
+        <v>0</v>
+      </c>
+      <c r="D58" s="26">
         <v>2</v>
       </c>
-      <c r="E58" s="24">
-        <v>1</v>
-      </c>
-      <c r="F58" s="24">
-        <v>1</v>
-      </c>
-      <c r="G58" s="24">
-        <v>0</v>
-      </c>
-      <c r="H58" s="24">
-        <v>1</v>
-      </c>
-      <c r="I58" s="24">
-        <v>0</v>
-      </c>
-      <c r="J58" s="24">
-        <v>0</v>
-      </c>
-      <c r="K58" s="24">
-        <v>0</v>
-      </c>
-      <c r="L58" s="24">
-        <v>1</v>
-      </c>
-      <c r="M58" s="24">
-        <v>0</v>
-      </c>
-      <c r="N58" s="24">
-        <v>1</v>
-      </c>
-      <c r="O58" s="24">
+      <c r="E58" s="26">
+        <v>1</v>
+      </c>
+      <c r="F58" s="26">
+        <v>1</v>
+      </c>
+      <c r="G58" s="26">
+        <v>0</v>
+      </c>
+      <c r="H58" s="26">
+        <v>1</v>
+      </c>
+      <c r="I58" s="26">
+        <v>0</v>
+      </c>
+      <c r="J58" s="26">
+        <v>0</v>
+      </c>
+      <c r="K58" s="26">
+        <v>0</v>
+      </c>
+      <c r="L58" s="26">
+        <v>1</v>
+      </c>
+      <c r="M58" s="26">
+        <v>0</v>
+      </c>
+      <c r="N58" s="26">
+        <v>1</v>
+      </c>
+      <c r="O58" s="26">
         <v>0</v>
       </c>
     </row>
@@ -6235,46 +6364,46 @@
       <c r="A59" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B59" s="24">
-        <v>0</v>
-      </c>
-      <c r="C59" s="24">
-        <v>0</v>
-      </c>
-      <c r="D59" s="24">
-        <v>0</v>
-      </c>
-      <c r="E59" s="24">
-        <v>0</v>
-      </c>
-      <c r="F59" s="24">
-        <v>0</v>
-      </c>
-      <c r="G59" s="24">
-        <v>0</v>
-      </c>
-      <c r="H59" s="24">
-        <v>0</v>
-      </c>
-      <c r="I59" s="24">
-        <v>0</v>
-      </c>
-      <c r="J59" s="24">
-        <v>0</v>
-      </c>
-      <c r="K59" s="24">
-        <v>0</v>
-      </c>
-      <c r="L59" s="24">
-        <v>0</v>
-      </c>
-      <c r="M59" s="24">
-        <v>0</v>
-      </c>
-      <c r="N59" s="24">
-        <v>0</v>
-      </c>
-      <c r="O59" s="24">
+      <c r="B59" s="26">
+        <v>0</v>
+      </c>
+      <c r="C59" s="26">
+        <v>0</v>
+      </c>
+      <c r="D59" s="26">
+        <v>0</v>
+      </c>
+      <c r="E59" s="26">
+        <v>0</v>
+      </c>
+      <c r="F59" s="26">
+        <v>0</v>
+      </c>
+      <c r="G59" s="26">
+        <v>0</v>
+      </c>
+      <c r="H59" s="26">
+        <v>0</v>
+      </c>
+      <c r="I59" s="26">
+        <v>0</v>
+      </c>
+      <c r="J59" s="26">
+        <v>0</v>
+      </c>
+      <c r="K59" s="26">
+        <v>0</v>
+      </c>
+      <c r="L59" s="26">
+        <v>0</v>
+      </c>
+      <c r="M59" s="26">
+        <v>0</v>
+      </c>
+      <c r="N59" s="26">
+        <v>0</v>
+      </c>
+      <c r="O59" s="26">
         <v>0</v>
       </c>
     </row>
@@ -6282,46 +6411,46 @@
       <c r="A60" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B60" s="24">
-        <v>0</v>
-      </c>
-      <c r="C60" s="24">
-        <v>0</v>
-      </c>
-      <c r="D60" s="24">
-        <v>0</v>
-      </c>
-      <c r="E60" s="24">
-        <v>0</v>
-      </c>
-      <c r="F60" s="24">
-        <v>0</v>
-      </c>
-      <c r="G60" s="24">
-        <v>0</v>
-      </c>
-      <c r="H60" s="24">
-        <v>0</v>
-      </c>
-      <c r="I60" s="24">
-        <v>0</v>
-      </c>
-      <c r="J60" s="24">
-        <v>0</v>
-      </c>
-      <c r="K60" s="24">
-        <v>0</v>
-      </c>
-      <c r="L60" s="24">
-        <v>0</v>
-      </c>
-      <c r="M60" s="24">
-        <v>0</v>
-      </c>
-      <c r="N60" s="24">
-        <v>0</v>
-      </c>
-      <c r="O60" s="24">
+      <c r="B60" s="26">
+        <v>0</v>
+      </c>
+      <c r="C60" s="26">
+        <v>0</v>
+      </c>
+      <c r="D60" s="26">
+        <v>0</v>
+      </c>
+      <c r="E60" s="26">
+        <v>0</v>
+      </c>
+      <c r="F60" s="26">
+        <v>0</v>
+      </c>
+      <c r="G60" s="26">
+        <v>0</v>
+      </c>
+      <c r="H60" s="26">
+        <v>0</v>
+      </c>
+      <c r="I60" s="26">
+        <v>0</v>
+      </c>
+      <c r="J60" s="26">
+        <v>0</v>
+      </c>
+      <c r="K60" s="26">
+        <v>0</v>
+      </c>
+      <c r="L60" s="26">
+        <v>0</v>
+      </c>
+      <c r="M60" s="26">
+        <v>0</v>
+      </c>
+      <c r="N60" s="26">
+        <v>0</v>
+      </c>
+      <c r="O60" s="26">
         <v>0</v>
       </c>
     </row>
@@ -6329,46 +6458,46 @@
       <c r="A61" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B61" s="24">
-        <v>0</v>
-      </c>
-      <c r="C61" s="24">
-        <v>0</v>
-      </c>
-      <c r="D61" s="24">
-        <v>0</v>
-      </c>
-      <c r="E61" s="24">
-        <v>0</v>
-      </c>
-      <c r="F61" s="24">
-        <v>0</v>
-      </c>
-      <c r="G61" s="24">
-        <v>0</v>
-      </c>
-      <c r="H61" s="24">
-        <v>0</v>
-      </c>
-      <c r="I61" s="24">
-        <v>0</v>
-      </c>
-      <c r="J61" s="24">
-        <v>0</v>
-      </c>
-      <c r="K61" s="24">
-        <v>0</v>
-      </c>
-      <c r="L61" s="24">
-        <v>0</v>
-      </c>
-      <c r="M61" s="24">
-        <v>0</v>
-      </c>
-      <c r="N61" s="24">
-        <v>0</v>
-      </c>
-      <c r="O61" s="24">
+      <c r="B61" s="26">
+        <v>0</v>
+      </c>
+      <c r="C61" s="26">
+        <v>0</v>
+      </c>
+      <c r="D61" s="26">
+        <v>0</v>
+      </c>
+      <c r="E61" s="26">
+        <v>0</v>
+      </c>
+      <c r="F61" s="26">
+        <v>0</v>
+      </c>
+      <c r="G61" s="26">
+        <v>0</v>
+      </c>
+      <c r="H61" s="26">
+        <v>0</v>
+      </c>
+      <c r="I61" s="26">
+        <v>0</v>
+      </c>
+      <c r="J61" s="26">
+        <v>0</v>
+      </c>
+      <c r="K61" s="26">
+        <v>0</v>
+      </c>
+      <c r="L61" s="26">
+        <v>0</v>
+      </c>
+      <c r="M61" s="26">
+        <v>0</v>
+      </c>
+      <c r="N61" s="26">
+        <v>0</v>
+      </c>
+      <c r="O61" s="26">
         <v>0</v>
       </c>
     </row>
@@ -6376,46 +6505,46 @@
       <c r="A62" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B62" s="24">
-        <v>0</v>
-      </c>
-      <c r="C62" s="24">
-        <v>0</v>
-      </c>
-      <c r="D62" s="24">
-        <v>0</v>
-      </c>
-      <c r="E62" s="24">
-        <v>0</v>
-      </c>
-      <c r="F62" s="24">
-        <v>0</v>
-      </c>
-      <c r="G62" s="24">
-        <v>0</v>
-      </c>
-      <c r="H62" s="24">
-        <v>0</v>
-      </c>
-      <c r="I62" s="24">
-        <v>0</v>
-      </c>
-      <c r="J62" s="24">
-        <v>0</v>
-      </c>
-      <c r="K62" s="24">
-        <v>0</v>
-      </c>
-      <c r="L62" s="24">
-        <v>0</v>
-      </c>
-      <c r="M62" s="24">
-        <v>0</v>
-      </c>
-      <c r="N62" s="24">
-        <v>0</v>
-      </c>
-      <c r="O62" s="24">
+      <c r="B62" s="26">
+        <v>0</v>
+      </c>
+      <c r="C62" s="26">
+        <v>0</v>
+      </c>
+      <c r="D62" s="26">
+        <v>0</v>
+      </c>
+      <c r="E62" s="26">
+        <v>0</v>
+      </c>
+      <c r="F62" s="26">
+        <v>0</v>
+      </c>
+      <c r="G62" s="26">
+        <v>0</v>
+      </c>
+      <c r="H62" s="26">
+        <v>0</v>
+      </c>
+      <c r="I62" s="26">
+        <v>0</v>
+      </c>
+      <c r="J62" s="26">
+        <v>0</v>
+      </c>
+      <c r="K62" s="26">
+        <v>0</v>
+      </c>
+      <c r="L62" s="26">
+        <v>0</v>
+      </c>
+      <c r="M62" s="26">
+        <v>0</v>
+      </c>
+      <c r="N62" s="26">
+        <v>0</v>
+      </c>
+      <c r="O62" s="26">
         <v>0</v>
       </c>
     </row>
@@ -6423,46 +6552,46 @@
       <c r="A63" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B63" s="24">
-        <v>0</v>
-      </c>
-      <c r="C63" s="24">
-        <v>0</v>
-      </c>
-      <c r="D63" s="24">
-        <v>0</v>
-      </c>
-      <c r="E63" s="24">
-        <v>0</v>
-      </c>
-      <c r="F63" s="24">
-        <v>1</v>
-      </c>
-      <c r="G63" s="24">
-        <v>0</v>
-      </c>
-      <c r="H63" s="24">
-        <v>0</v>
-      </c>
-      <c r="I63" s="24">
-        <v>0</v>
-      </c>
-      <c r="J63" s="24">
-        <v>0</v>
-      </c>
-      <c r="K63" s="24">
-        <v>0</v>
-      </c>
-      <c r="L63" s="24">
-        <v>1</v>
-      </c>
-      <c r="M63" s="24">
-        <v>1</v>
-      </c>
-      <c r="N63" s="24">
-        <v>0</v>
-      </c>
-      <c r="O63" s="24">
+      <c r="B63" s="26">
+        <v>0</v>
+      </c>
+      <c r="C63" s="26">
+        <v>0</v>
+      </c>
+      <c r="D63" s="26">
+        <v>0</v>
+      </c>
+      <c r="E63" s="26">
+        <v>0</v>
+      </c>
+      <c r="F63" s="26">
+        <v>1</v>
+      </c>
+      <c r="G63" s="26">
+        <v>0</v>
+      </c>
+      <c r="H63" s="26">
+        <v>0</v>
+      </c>
+      <c r="I63" s="26">
+        <v>0</v>
+      </c>
+      <c r="J63" s="26">
+        <v>0</v>
+      </c>
+      <c r="K63" s="26">
+        <v>0</v>
+      </c>
+      <c r="L63" s="26">
+        <v>1</v>
+      </c>
+      <c r="M63" s="26">
+        <v>1</v>
+      </c>
+      <c r="N63" s="26">
+        <v>0</v>
+      </c>
+      <c r="O63" s="26">
         <v>1</v>
       </c>
     </row>
@@ -6470,46 +6599,46 @@
       <c r="A64" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B64" s="24">
-        <v>0</v>
-      </c>
-      <c r="C64" s="24">
-        <v>0</v>
-      </c>
-      <c r="D64" s="24">
-        <v>0</v>
-      </c>
-      <c r="E64" s="24">
-        <v>1</v>
-      </c>
-      <c r="F64" s="24">
-        <v>0</v>
-      </c>
-      <c r="G64" s="24">
-        <v>0</v>
-      </c>
-      <c r="H64" s="24">
-        <v>0</v>
-      </c>
-      <c r="I64" s="24">
-        <v>1</v>
-      </c>
-      <c r="J64" s="24">
-        <v>1</v>
-      </c>
-      <c r="K64" s="24">
-        <v>0</v>
-      </c>
-      <c r="L64" s="24">
-        <v>0</v>
-      </c>
-      <c r="M64" s="24">
-        <v>0</v>
-      </c>
-      <c r="N64" s="24">
-        <v>1</v>
-      </c>
-      <c r="O64" s="24">
+      <c r="B64" s="26">
+        <v>0</v>
+      </c>
+      <c r="C64" s="26">
+        <v>0</v>
+      </c>
+      <c r="D64" s="26">
+        <v>0</v>
+      </c>
+      <c r="E64" s="26">
+        <v>1</v>
+      </c>
+      <c r="F64" s="26">
+        <v>0</v>
+      </c>
+      <c r="G64" s="26">
+        <v>0</v>
+      </c>
+      <c r="H64" s="26">
+        <v>0</v>
+      </c>
+      <c r="I64" s="26">
+        <v>1</v>
+      </c>
+      <c r="J64" s="26">
+        <v>1</v>
+      </c>
+      <c r="K64" s="26">
+        <v>0</v>
+      </c>
+      <c r="L64" s="26">
+        <v>0</v>
+      </c>
+      <c r="M64" s="26">
+        <v>0</v>
+      </c>
+      <c r="N64" s="26">
+        <v>1</v>
+      </c>
+      <c r="O64" s="26">
         <v>1</v>
       </c>
     </row>
@@ -6517,46 +6646,46 @@
       <c r="A65" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B65" s="24">
-        <v>0</v>
-      </c>
-      <c r="C65" s="24">
-        <v>1</v>
-      </c>
-      <c r="D65" s="24">
+      <c r="B65" s="26">
+        <v>0</v>
+      </c>
+      <c r="C65" s="26">
+        <v>1</v>
+      </c>
+      <c r="D65" s="26">
         <v>2</v>
       </c>
-      <c r="E65" s="24">
-        <v>0</v>
-      </c>
-      <c r="F65" s="24">
-        <v>0</v>
-      </c>
-      <c r="G65" s="24">
-        <v>0</v>
-      </c>
-      <c r="H65" s="24">
-        <v>0</v>
-      </c>
-      <c r="I65" s="24">
-        <v>0</v>
-      </c>
-      <c r="J65" s="24">
-        <v>0</v>
-      </c>
-      <c r="K65" s="24">
-        <v>0</v>
-      </c>
-      <c r="L65" s="24">
-        <v>0</v>
-      </c>
-      <c r="M65" s="24">
-        <v>0</v>
-      </c>
-      <c r="N65" s="24">
-        <v>0</v>
-      </c>
-      <c r="O65" s="24">
+      <c r="E65" s="26">
+        <v>0</v>
+      </c>
+      <c r="F65" s="26">
+        <v>0</v>
+      </c>
+      <c r="G65" s="26">
+        <v>0</v>
+      </c>
+      <c r="H65" s="26">
+        <v>0</v>
+      </c>
+      <c r="I65" s="26">
+        <v>0</v>
+      </c>
+      <c r="J65" s="26">
+        <v>0</v>
+      </c>
+      <c r="K65" s="26">
+        <v>0</v>
+      </c>
+      <c r="L65" s="26">
+        <v>0</v>
+      </c>
+      <c r="M65" s="26">
+        <v>0</v>
+      </c>
+      <c r="N65" s="26">
+        <v>0</v>
+      </c>
+      <c r="O65" s="26">
         <v>0</v>
       </c>
     </row>
@@ -6564,65 +6693,65 @@
       <c r="A66" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B66" s="24">
-        <v>0</v>
-      </c>
-      <c r="C66" s="24">
-        <v>0</v>
-      </c>
-      <c r="D66" s="24">
-        <v>0</v>
-      </c>
-      <c r="E66" s="24">
-        <v>0</v>
-      </c>
-      <c r="F66" s="24">
-        <v>0</v>
-      </c>
-      <c r="G66" s="24">
-        <v>0</v>
-      </c>
-      <c r="H66" s="24">
-        <v>0</v>
-      </c>
-      <c r="I66" s="24">
-        <v>0</v>
-      </c>
-      <c r="J66" s="24">
-        <v>0</v>
-      </c>
-      <c r="K66" s="24">
-        <v>0</v>
-      </c>
-      <c r="L66" s="24">
-        <v>0</v>
-      </c>
-      <c r="M66" s="24">
-        <v>0</v>
-      </c>
-      <c r="N66" s="24">
-        <v>0</v>
-      </c>
-      <c r="O66" s="24">
+      <c r="B66" s="26">
+        <v>0</v>
+      </c>
+      <c r="C66" s="26">
+        <v>0</v>
+      </c>
+      <c r="D66" s="26">
+        <v>0</v>
+      </c>
+      <c r="E66" s="26">
+        <v>0</v>
+      </c>
+      <c r="F66" s="26">
+        <v>0</v>
+      </c>
+      <c r="G66" s="26">
+        <v>0</v>
+      </c>
+      <c r="H66" s="26">
+        <v>0</v>
+      </c>
+      <c r="I66" s="26">
+        <v>0</v>
+      </c>
+      <c r="J66" s="26">
+        <v>0</v>
+      </c>
+      <c r="K66" s="26">
+        <v>0</v>
+      </c>
+      <c r="L66" s="26">
+        <v>0</v>
+      </c>
+      <c r="M66" s="26">
+        <v>0</v>
+      </c>
+      <c r="N66" s="26">
+        <v>0</v>
+      </c>
+      <c r="O66" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:15">
-      <c r="A68" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
+      <c r="A68" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="23"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="23"/>
+      <c r="K68" s="23"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="23"/>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="6" t="s">
@@ -6668,7 +6797,7 @@
         <v>43</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:15">
@@ -7142,21 +7271,21 @@
       </c>
     </row>
     <row r="81" spans="1:15">
-      <c r="A81" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B81" s="21"/>
-      <c r="C81" s="21"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
-      <c r="J81" s="21"/>
-      <c r="K81" s="21"/>
-      <c r="L81" s="21"/>
-      <c r="M81" s="21"/>
+      <c r="A81" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B81" s="23"/>
+      <c r="C81" s="23"/>
+      <c r="D81" s="23"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="23"/>
+      <c r="G81" s="23"/>
+      <c r="H81" s="23"/>
+      <c r="I81" s="23"/>
+      <c r="J81" s="23"/>
+      <c r="K81" s="23"/>
+      <c r="L81" s="23"/>
+      <c r="M81" s="23"/>
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="6" t="s">
@@ -7202,7 +7331,7 @@
         <v>43</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:15">
@@ -7676,21 +7805,21 @@
       </c>
     </row>
     <row r="94" spans="1:15">
-      <c r="A94" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B94" s="21"/>
-      <c r="C94" s="21"/>
-      <c r="D94" s="21"/>
-      <c r="E94" s="21"/>
-      <c r="F94" s="21"/>
-      <c r="G94" s="21"/>
-      <c r="H94" s="21"/>
-      <c r="I94" s="21"/>
-      <c r="J94" s="21"/>
-      <c r="K94" s="21"/>
-      <c r="L94" s="21"/>
-      <c r="M94" s="21"/>
+      <c r="A94" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B94" s="23"/>
+      <c r="C94" s="23"/>
+      <c r="D94" s="23"/>
+      <c r="E94" s="23"/>
+      <c r="F94" s="23"/>
+      <c r="G94" s="23"/>
+      <c r="H94" s="23"/>
+      <c r="I94" s="23"/>
+      <c r="J94" s="23"/>
+      <c r="K94" s="23"/>
+      <c r="L94" s="23"/>
+      <c r="M94" s="23"/>
     </row>
     <row r="95" spans="1:15">
       <c r="A95" s="6" t="s">
@@ -7736,7 +7865,7 @@
         <v>43</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:15">
@@ -8210,21 +8339,21 @@
       </c>
     </row>
     <row r="107" spans="1:15">
-      <c r="A107" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B107" s="21"/>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
-      <c r="I107" s="21"/>
-      <c r="J107" s="21"/>
-      <c r="K107" s="21"/>
-      <c r="L107" s="21"/>
-      <c r="M107" s="21"/>
+      <c r="A107" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B107" s="23"/>
+      <c r="C107" s="23"/>
+      <c r="D107" s="23"/>
+      <c r="E107" s="23"/>
+      <c r="F107" s="23"/>
+      <c r="G107" s="23"/>
+      <c r="H107" s="23"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="23"/>
+      <c r="K107" s="23"/>
+      <c r="L107" s="23"/>
+      <c r="M107" s="23"/>
     </row>
     <row r="108" spans="1:15">
       <c r="A108" s="6" t="s">
@@ -8270,7 +8399,7 @@
         <v>43</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:15">
@@ -8766,29 +8895,31 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="13" width="9.7109375" customWidth="1"/>
+    <col min="2" max="15" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1">
-      <c r="A1" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
+      <c r="A1" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>31</v>
@@ -8830,7 +8961,7 @@
         <v>43</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -8937,7 +9068,7 @@
       <c r="C6" s="11">
         <v>0.2700657835853922</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="11">
         <v>0.4460744555188425</v>
       </c>
@@ -8959,31 +9090,31 @@
       <c r="K6" s="11">
         <v>0.9985489020025152</v>
       </c>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="11">
         <v>1.26597879048438</v>
       </c>
       <c r="D7" s="11">
         <v>0.8469549467964682</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="24"/>
       <c r="F7" s="11">
         <v>0</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
       <c r="L7" s="11">
         <v>1.308515426021579</v>
       </c>
@@ -9025,14 +9156,14 @@
       <c r="I8" s="11">
         <v>1.197524627431169</v>
       </c>
-      <c r="J8" s="22"/>
+      <c r="J8" s="24"/>
       <c r="K8" s="11">
         <v>0</v>
       </c>
       <c r="L8" s="11">
         <v>0.4490783646250567</v>
       </c>
-      <c r="M8" s="22"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="11">
         <v>0</v>
       </c>
@@ -9044,22 +9175,22 @@
       <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="11">
         <v>1.111181821873858</v>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="24"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="10" t="s">
@@ -9098,7 +9229,7 @@
       <c r="L10" s="11">
         <v>0.7297423746679665</v>
       </c>
-      <c r="M10" s="22"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="11">
         <v>0.6001238280558995</v>
       </c>
@@ -9110,18 +9241,18 @@
       <c r="A11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="22"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="11">
         <v>0.7433949691820756</v>
       </c>
       <c r="D11" s="11">
         <v>0</v>
       </c>
-      <c r="E11" s="22"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="11">
         <v>0.9661026054257319</v>
       </c>
-      <c r="G11" s="22"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="11">
         <v>0</v>
       </c>
@@ -9198,26 +9329,26 @@
       <c r="A13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
       <c r="O13" s="11">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/prolongation_report.xlsx
+++ b/prolongation_report.xlsx
@@ -4046,7 +4046,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="13" width="10.7109375" customWidth="1"/>
+    <col min="2" max="15" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1">
@@ -4065,6 +4065,8 @@
       <c r="K1" s="20"/>
       <c r="L1" s="20"/>
       <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="23" t="s">
@@ -4082,6 +4084,8 @@
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="6" t="s">
@@ -4616,6 +4620,8 @@
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
       <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="6" t="s">
@@ -5150,6 +5156,8 @@
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
       <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="6" t="s">
@@ -5684,6 +5692,8 @@
       <c r="K42" s="23"/>
       <c r="L42" s="23"/>
       <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="6" t="s">
@@ -6218,6 +6228,8 @@
       <c r="K55" s="23"/>
       <c r="L55" s="23"/>
       <c r="M55" s="23"/>
+      <c r="N55" s="23"/>
+      <c r="O55" s="23"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="6" t="s">
@@ -6752,6 +6764,8 @@
       <c r="K68" s="23"/>
       <c r="L68" s="23"/>
       <c r="M68" s="23"/>
+      <c r="N68" s="23"/>
+      <c r="O68" s="23"/>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="6" t="s">
@@ -7286,6 +7300,8 @@
       <c r="K81" s="23"/>
       <c r="L81" s="23"/>
       <c r="M81" s="23"/>
+      <c r="N81" s="23"/>
+      <c r="O81" s="23"/>
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="6" t="s">
@@ -7820,6 +7836,8 @@
       <c r="K94" s="23"/>
       <c r="L94" s="23"/>
       <c r="M94" s="23"/>
+      <c r="N94" s="23"/>
+      <c r="O94" s="23"/>
     </row>
     <row r="95" spans="1:15">
       <c r="A95" s="6" t="s">
@@ -8354,6 +8372,8 @@
       <c r="K107" s="23"/>
       <c r="L107" s="23"/>
       <c r="M107" s="23"/>
+      <c r="N107" s="23"/>
+      <c r="O107" s="23"/>
     </row>
     <row r="108" spans="1:15">
       <c r="A108" s="6" t="s">
@@ -8874,16 +8894,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="A42:M42"/>
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="A68:M68"/>
-    <mergeCell ref="A81:M81"/>
-    <mergeCell ref="A94:M94"/>
-    <mergeCell ref="A107:M107"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A42:O42"/>
+    <mergeCell ref="A55:O55"/>
+    <mergeCell ref="A68:O68"/>
+    <mergeCell ref="A81:O81"/>
+    <mergeCell ref="A94:O94"/>
+    <mergeCell ref="A107:O107"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
